--- a/output/pdf_financials_xlsx/CXC.xlsx
+++ b/output/pdf_financials_xlsx/CXC.xlsx
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.001637</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001135</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.017063</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.001637</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001135</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.017063</v>
       </c>
     </row>
     <row r="37">
@@ -1209,10 +1209,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.001135</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.040239</v>
+        <v>0.023176</v>
       </c>
     </row>
     <row r="49">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/CXC.xlsx
+++ b/output/pdf_financials_xlsx/CXC.xlsx
@@ -3428,7 +3428,11 @@
           <t>Deferred tax recovery (note 15)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -4050,7 +4054,11 @@
           <t>Net Income (loss) $</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
         <v>-0.321199</v>
       </c>
